--- a/tame_output/ON/bt/strategyON_20240227.xlsx
+++ b/tame_output/ON/bt/strategyON_20240227.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,17 +949,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.5%</t>
+          <t>446.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-21.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,15 +1285,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.0%</t>
+          <t>129.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>1.019632069058828</v>
+        <v>0.8979180577453039</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.52664996175575</v>
+        <v>3.47796435723034</v>
       </c>
       <c r="F1846" t="n">
-        <v>2.113187876201311</v>
+        <v>1.991473864887787</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.387066284166753</v>
+        <v>4.314037877378638</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>1.027175064405681</v>
+        <v>0.9054610530921569</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.527594051399555</v>
+        <v>3.478908446874145</v>
       </c>
       <c r="F1847" t="n">
-        <v>2.120730871548164</v>
+        <v>1.99901686023464</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.389518972879928</v>
+        <v>4.316490566091813</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>1.029154021099912</v>
+        <v>0.9074400097863878</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.528251850676169</v>
+        <v>3.479566246150759</v>
       </c>
       <c r="F1848" t="n">
-        <v>2.121790271509738</v>
+        <v>2.000076260196213</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.390020829455795</v>
+        <v>4.316992422667679</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>1.026963256647418</v>
+        <v>0.9052492453338941</v>
       </c>
       <c r="E1849" t="n">
-        <v>3.532267689449097</v>
+        <v>3.483582084923687</v>
       </c>
       <c r="F1849" t="n">
-        <v>2.121790271509738</v>
+        <v>2.000076260196213</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.394912974009719</v>
+        <v>4.321884567221605</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>1.036264654648701</v>
+        <v>0.9145506433351769</v>
       </c>
       <c r="E1850" t="n">
-        <v>3.531069704987598</v>
+        <v>3.482384100462188</v>
       </c>
       <c r="F1850" t="n">
-        <v>2.13109166951102</v>
+        <v>2.009377658197496</v>
       </c>
       <c r="G1850" t="n">
-        <v>4.395575269148477</v>
+        <v>4.322546862360363</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>1.029629732151771</v>
+        <v>0.9079157208382467</v>
       </c>
       <c r="E1851" t="n">
-        <v>3.521500035295275</v>
+        <v>3.472814430769865</v>
       </c>
       <c r="F1851" t="n">
-        <v>2.12445674701409</v>
+        <v>2.002742735700566</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.384678614956768</v>
+        <v>4.311650208168654</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>1.03670191585822</v>
+        <v>0.9149879045446961</v>
       </c>
       <c r="E1852" t="n">
-        <v>3.544667198516623</v>
+        <v>3.495981593991213</v>
       </c>
       <c r="F1852" t="n">
-        <v>2.13152893072054</v>
+        <v>2.009814919407016</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.409260214919406</v>
+        <v>4.336231808131291</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>1.040038662367192</v>
+        <v>0.9183246510536678</v>
       </c>
       <c r="E1853" t="n">
-        <v>3.55410064752878</v>
+        <v>3.50541504300337</v>
       </c>
       <c r="F1853" t="n">
-        <v>2.134220963139571</v>
+        <v>2.012506951826047</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.418974184779393</v>
+        <v>4.345945777991279</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>1.038585995904082</v>
+        <v>0.9168719845905585</v>
       </c>
       <c r="E1854" t="n">
-        <v>3.554625972987268</v>
+        <v>3.505940368461859</v>
       </c>
       <c r="F1854" t="n">
-        <v>2.132768296676462</v>
+        <v>2.011054285362938</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.41920897694526</v>
+        <v>4.346180570157146</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>1.038155296855487</v>
+        <v>0.916441285541963</v>
       </c>
       <c r="E1855" t="n">
-        <v>3.552996232180694</v>
+        <v>3.504310627655284</v>
       </c>
       <c r="F1855" t="n">
-        <v>2.132768296676462</v>
+        <v>2.011054285362938</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.417751515758123</v>
+        <v>4.344723108970009</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>1.037318119873652</v>
+        <v>0.9156041085601279</v>
       </c>
       <c r="E1856" t="n">
-        <v>3.554430484842576</v>
+        <v>3.505744880317166</v>
       </c>
       <c r="F1856" t="n">
-        <v>2.131814045414591</v>
+        <v>2.010100034101066</v>
       </c>
       <c r="G1856" t="n">
-        <v>4.418948088455616</v>
+        <v>4.345919681667502</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>1.025813634875367</v>
+        <v>0.9040996235618428</v>
       </c>
       <c r="E1857" t="n">
-        <v>3.545934749499519</v>
+        <v>3.49724914497411</v>
       </c>
       <c r="F1857" t="n">
-        <v>2.120309560416306</v>
+        <v>1.998595549102781</v>
       </c>
       <c r="G1857" t="n">
-        <v>4.408151456112903</v>
+        <v>4.335123049324789</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>1.019152694653219</v>
+        <v>0.897438683339695</v>
       </c>
       <c r="E1858" t="n">
-        <v>3.54504330011092</v>
+        <v>3.49635769558551</v>
       </c>
       <c r="F1858" t="n">
-        <v>2.120309560416306</v>
+        <v>1.998595549102781</v>
       </c>
       <c r="G1858" t="n">
-        <v>4.409924382813163</v>
+        <v>4.336895976025049</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>1.017002174873008</v>
+        <v>0.8952881635594837</v>
       </c>
       <c r="E1859" t="n">
-        <v>3.53051597966624</v>
+        <v>3.48183037514083</v>
       </c>
       <c r="F1859" t="n">
-        <v>2.118661552577707</v>
+        <v>1.996947541264183</v>
       </c>
       <c r="G1859" t="n">
-        <v>4.395268465577408</v>
+        <v>4.322240058789294</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>1.030064429221975</v>
+        <v>0.9083504179084514</v>
       </c>
       <c r="E1860" t="n">
-        <v>3.524025656407917</v>
+        <v>3.475340051882508</v>
       </c>
       <c r="F1860" t="n">
-        <v>2.124496099367774</v>
+        <v>2.00278208805425</v>
       </c>
       <c r="G1860" t="n">
-        <v>4.387053968653539</v>
+        <v>4.314025561865424</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>1.028500278111672</v>
+        <v>0.9067862667981483</v>
       </c>
       <c r="E1861" t="n">
-        <v>3.521980587619761</v>
+        <v>3.473294983094352</v>
       </c>
       <c r="F1861" t="n">
-        <v>2.124496099367774</v>
+        <v>2.00278208805425</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.385634560309504</v>
+        <v>4.31260615352139</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>1.030548862973383</v>
+        <v>0.908834851659859</v>
       </c>
       <c r="E1862" t="n">
-        <v>3.529287581798687</v>
+        <v>3.480601977273277</v>
       </c>
       <c r="F1862" t="n">
-        <v>2.126743799425966</v>
+        <v>2.005029788112442</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.393470740578661</v>
+        <v>4.320442333790547</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>1.032975927502101</v>
+        <v>0.9112619161885773</v>
       </c>
       <c r="E1863" t="n">
-        <v>3.529512922616006</v>
+        <v>3.480827318090596</v>
       </c>
       <c r="F1863" t="n">
-        <v>2.126411017618814</v>
+        <v>2.00469700630529</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.392525586500201</v>
+        <v>4.319497179712087</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>1.031683905727763</v>
+        <v>0.9099698944142393</v>
       </c>
       <c r="E1864" t="n">
-        <v>3.52775765792103</v>
+        <v>3.47907205339562</v>
       </c>
       <c r="F1864" t="n">
-        <v>2.125118995844476</v>
+        <v>2.003404984530952</v>
       </c>
       <c r="G1864" t="n">
-        <v>4.390511917450358</v>
+        <v>4.317483510662243</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>1.026869313472922</v>
+        <v>0.9051553021593979</v>
       </c>
       <c r="E1865" t="n">
-        <v>3.521017253490554</v>
+        <v>3.472331648965144</v>
       </c>
       <c r="F1865" t="n">
-        <v>2.125118995844476</v>
+        <v>2.003404984530952</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.385697349921818</v>
+        <v>4.312668943133704</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>1.030026014503126</v>
+        <v>0.9083120031896018</v>
       </c>
       <c r="E1866" t="n">
-        <v>3.520273984511513</v>
+        <v>3.471588379986103</v>
       </c>
       <c r="F1866" t="n">
-        <v>2.125118995844476</v>
+        <v>2.003404984530952</v>
       </c>
       <c r="G1866" t="n">
-        <v>4.383691400530696</v>
+        <v>4.310662993742581</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>1.026012982090604</v>
+        <v>0.90429897077708</v>
       </c>
       <c r="E1867" t="n">
-        <v>3.528927462215183</v>
+        <v>3.480241857689773</v>
       </c>
       <c r="F1867" t="n">
-        <v>2.125118995844476</v>
+        <v>2.003404984530952</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.393950091199375</v>
+        <v>4.32092168441126</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>1.012298117765493</v>
+        <v>0.8905841064519684</v>
       </c>
       <c r="E1868" t="n">
-        <v>3.519541081630834</v>
+        <v>3.470855477105424</v>
       </c>
       <c r="F1868" t="n">
-        <v>2.125118995844476</v>
+        <v>2.003404984530952</v>
       </c>
       <c r="G1868" t="n">
-        <v>4.39004965634507</v>
+        <v>4.317021249556955</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>1.006781197921526</v>
+        <v>0.885067186608002</v>
       </c>
       <c r="E1869" t="n">
-        <v>3.515739233748248</v>
+        <v>3.467053629222838</v>
       </c>
       <c r="F1869" t="n">
-        <v>2.125118995844476</v>
+        <v>2.003404984530952</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.388454576400071</v>
+        <v>4.315426169611956</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>1.00196815945619</v>
+        <v>0.8802541481426652</v>
       </c>
       <c r="E1870" t="n">
-        <v>3.517592994291322</v>
+        <v>3.468907389765912</v>
       </c>
       <c r="F1870" t="n">
-        <v>2.123572361141691</v>
+        <v>2.001858349828166</v>
       </c>
       <c r="G1870" t="n">
-        <v>4.391305571507607</v>
+        <v>4.318277164719493</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>1.004085318180483</v>
+        <v>0.8823713068669581</v>
       </c>
       <c r="E1871" t="n">
-        <v>3.514413553246635</v>
+        <v>3.465727948721226</v>
       </c>
       <c r="F1871" t="n">
-        <v>2.123572361141691</v>
+        <v>2.001858349828166</v>
       </c>
       <c r="G1871" t="n">
-        <v>4.387279266973204</v>
+        <v>4.31425086018509</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>1.004562664758972</v>
+        <v>0.8828486534454478</v>
       </c>
       <c r="E1872" t="n">
-        <v>3.514502390556447</v>
+        <v>3.465816786031038</v>
       </c>
       <c r="F1872" t="n">
-        <v>2.123572361141691</v>
+        <v>2.001858349828166</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.38717716565162</v>
+        <v>4.314148758863506</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>1.00558745106583</v>
+        <v>0.8838734397523054</v>
       </c>
       <c r="E1873" t="n">
-        <v>3.517483821050621</v>
+        <v>3.468798216525211</v>
       </c>
       <c r="F1873" t="n">
-        <v>2.124597147448548</v>
+        <v>2.002883136135024</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.390363553407165</v>
+        <v>4.31733514661905</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>0.9868460708069111</v>
+        <v>0.8651320594933867</v>
       </c>
       <c r="E1874" t="n">
-        <v>3.515337572245103</v>
+        <v>3.466651967719693</v>
       </c>
       <c r="F1874" t="n">
-        <v>2.124597147448548</v>
+        <v>2.002883136135024</v>
       </c>
       <c r="G1874" t="n">
-        <v>4.395713856705215</v>
+        <v>4.322685449917101</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>0.9738767280218126</v>
+        <v>0.8521627167082881</v>
       </c>
       <c r="E1875" t="n">
-        <v>3.518065855088242</v>
+        <v>3.469380250562832</v>
       </c>
       <c r="F1875" t="n">
-        <v>2.11162780466345</v>
+        <v>1.989913793349925</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.395848270991333</v>
+        <v>4.322819864203219</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>0.9803528748153721</v>
+        <v>0.8586388635018477</v>
       </c>
       <c r="E1876" t="n">
-        <v>3.523698064427434</v>
+        <v>3.475012459902024</v>
       </c>
       <c r="F1876" t="n">
-        <v>2.118103951457009</v>
+        <v>1.996389940143485</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.402775709689238</v>
+        <v>4.329747302901124</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>0.9840437997717835</v>
+        <v>0.862329788458259</v>
       </c>
       <c r="E1877" t="n">
-        <v>3.525174434409998</v>
+        <v>3.476488829884589</v>
       </c>
       <c r="F1877" t="n">
-        <v>2.118103951457009</v>
+        <v>1.996389940143485</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.402775709689238</v>
+        <v>4.329747302901124</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>0.9912591526435992</v>
+        <v>0.8695451413300748</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.533573772677367</v>
+        <v>3.484888168151957</v>
       </c>
       <c r="F1878" t="n">
-        <v>2.187882186747391</v>
+        <v>2.066168175433867</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.45015584798211</v>
+        <v>4.377127441193995</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>1.042286998725425</v>
+        <v>0.9205729874119009</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.558467465594534</v>
+        <v>3.509781861069124</v>
       </c>
       <c r="F1879" t="n">
-        <v>2.263091525054492</v>
+        <v>2.141377513740968</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.499764005450807</v>
+        <v>4.426735598662692</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>1.115756830392874</v>
+        <v>0.9940428190793493</v>
       </c>
       <c r="E1880" t="n">
-        <v>3.603227099754934</v>
+        <v>3.554541495229524</v>
       </c>
       <c r="F1880" t="n">
-        <v>2.336561356721941</v>
+        <v>2.214847345408416</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.559217605944696</v>
+        <v>4.486189199156582</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>1.196129185856804</v>
+        <v>1.074415174543279</v>
       </c>
       <c r="E1881" t="n">
-        <v>3.649931262688023</v>
+        <v>3.601245658162613</v>
       </c>
       <c r="F1881" t="n">
-        <v>2.41693371218587</v>
+        <v>2.295219700872346</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.621996239970571</v>
+        <v>4.548967833182457</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>1.229061055669654</v>
+        <v>1.10734704435613</v>
       </c>
       <c r="E1882" t="n">
-        <v>3.655884845711567</v>
+        <v>3.607199241186157</v>
       </c>
       <c r="F1882" t="n">
-        <v>2.41693371218587</v>
+        <v>2.295219700872346</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.614777075068975</v>
+        <v>4.54174866828086</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>1.208896414120107</v>
+        <v>1.087182402806582</v>
       </c>
       <c r="E1883" t="n">
-        <v>3.641146798317772</v>
+        <v>3.592461193792362</v>
       </c>
       <c r="F1883" t="n">
-        <v>2.396769070636323</v>
+        <v>2.275055059322799</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.596006099365271</v>
+        <v>4.522977692577156</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>1.267563344141641</v>
+        <v>1.145849332828116</v>
       </c>
       <c r="E1884" t="n">
-        <v>3.665729360164942</v>
+        <v>3.617043755639532</v>
       </c>
       <c r="F1884" t="n">
-        <v>2.481728539066461</v>
+        <v>2.360014527752937</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.64809757026191</v>
+        <v>4.575069163473795</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>1.33063257644798</v>
+        <v>1.208918565134455</v>
       </c>
       <c r="E1885" t="n">
-        <v>3.693650781716592</v>
+        <v>3.644965177191183</v>
       </c>
       <c r="F1885" t="n">
-        <v>2.453214976384226</v>
+        <v>2.331500965070702</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.633683161281684</v>
+        <v>4.560654754493569</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.329171599222734</v>
+        <v>3.322150052573061</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>1.411489171613405</v>
+        <v>1.403197206570238</v>
       </c>
       <c r="E1886" t="n">
-        <v>3.729983755469163</v>
+        <v>3.726666969451896</v>
       </c>
       <c r="F1886" t="n">
-        <v>2.453214976384226</v>
+        <v>2.331500965070702</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.637673496968084</v>
+        <v>4.56464509017997</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240227.xlsx
+++ b/tame_output/ON/bt/strategyON_20240227.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.9%</t>
+          <t>447.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-22.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
     </row>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>1.403197206570238</v>
+        <v>1.394964805704351</v>
       </c>
       <c r="E1886" t="n">
-        <v>3.726666969451896</v>
+        <v>3.723374009105541</v>
       </c>
       <c r="F1886" t="n">
         <v>2.331500965070702</v>

--- a/tame_output/ON/bt/strategyON_20240227.xlsx
+++ b/tame_output/ON/bt/strategyON_20240227.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.0%</t>
+          <t>448.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-35.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-9.2%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.322150052573061</v>
+        <v>3.32215005257306</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>1.394964805704351</v>
+        <v>1.260934079103268</v>
       </c>
       <c r="E1886" t="n">
-        <v>3.723374009105541</v>
+        <v>3.669761718465109</v>
       </c>
       <c r="F1886" t="n">
         <v>2.331500965070702</v>

--- a/tame_output/ON/bt/strategyON_20240227.xlsx
+++ b/tame_output/ON/bt/strategyON_20240227.xlsx
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.32215005257306</v>
+        <v>3.322150052573061</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
